--- a/data/trans_camb/P2A_lim_R-Habitat-trans_camb.xlsx
+++ b/data/trans_camb/P2A_lim_R-Habitat-trans_camb.xlsx
@@ -677,47 +677,47 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>1,37; 7,25</t>
+          <t>1,42; 7,15</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>1,01; 6,41</t>
+          <t>1,01; 6,25</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>6,3; 12,2</t>
+          <t>6,22; 12,27</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>3,11; 9,01</t>
+          <t>3,15; 8,98</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>0,99; 6,56</t>
+          <t>0,76; 6,39</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>4,75; 10,61</t>
+          <t>4,44; 10,34</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>3,2; 7,33</t>
+          <t>3,13; 7,29</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>1,66; 5,66</t>
+          <t>1,36; 5,57</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>6,22; 10,49</t>
+          <t>6,08; 10,57</t>
         </is>
       </c>
     </row>
@@ -783,47 +783,47 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>22,05; 179,16</t>
+          <t>20,95; 170,53</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>15,68; 164,04</t>
+          <t>14,88; 150,09</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>94,57; 303,1</t>
+          <t>98,28; 292,8</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>46,35; 206,98</t>
+          <t>45,7; 205,09</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>10,42; 152,22</t>
+          <t>9,28; 146,2</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>67,75; 249,56</t>
+          <t>65,64; 242,37</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>50,74; 164,51</t>
+          <t>49,26; 161,56</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>26,9; 128,1</t>
+          <t>22,22; 125,83</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>98,72; 228,66</t>
+          <t>98,06; 243,4</t>
         </is>
       </c>
     </row>
@@ -893,47 +893,47 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>0,23; 5,5</t>
+          <t>-0,03; 5,43</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>-2,82; 2,0</t>
+          <t>-2,76; 2,13</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>-2,5; 8,43</t>
+          <t>-1,52; 8,41</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>1,66; 7,47</t>
+          <t>1,54; 6,96</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>-1,45; 3,65</t>
+          <t>-1,6; 3,72</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>5,54; 10,77</t>
+          <t>5,71; 10,82</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>1,74; 5,49</t>
+          <t>1,7; 5,59</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>-1,31; 2,16</t>
+          <t>-1,32; 2,23</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>0,93; 8,41</t>
+          <t>1,88; 8,55</t>
         </is>
       </c>
     </row>
@@ -999,47 +999,47 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>3,23; 92,94</t>
+          <t>-1,93; 88,0</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>-33,1; 34,95</t>
+          <t>-32,51; 37,64</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>-18,5; 129,14</t>
+          <t>-17,6; 133,53</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>17,75; 110,25</t>
+          <t>15,63; 106,42</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>-16,07; 57,1</t>
+          <t>-16,72; 61,23</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>58,59; 164,74</t>
+          <t>62,14; 169,32</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>19,62; 83,07</t>
+          <t>20,39; 85,75</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>-16,35; 32,83</t>
+          <t>-15,7; 33,83</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>22,57; 123,81</t>
+          <t>23,75; 125,67</t>
         </is>
       </c>
     </row>
@@ -1109,47 +1109,47 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>-1,24; 4,62</t>
+          <t>-1,36; 4,78</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>-5,57; -0,39</t>
+          <t>-5,28; -0,01</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>5,2; 12,15</t>
+          <t>5,25; 12,17</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>-1,54; 4,84</t>
+          <t>-1,45; 4,76</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>-4,68; 1,13</t>
+          <t>-4,7; 0,95</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>4,92; 54,86</t>
+          <t>5,08; 60,09</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>-0,65; 3,65</t>
+          <t>-0,69; 3,66</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>-4,23; -0,25</t>
+          <t>-4,08; -0,27</t>
         </is>
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>6,61; 45,39</t>
+          <t>6,75; 44,87</t>
         </is>
       </c>
     </row>
@@ -1215,47 +1215,47 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>-14,97; 86,82</t>
+          <t>-16,03; 86,55</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>-63,4; -3,95</t>
+          <t>-61,85; 1,86</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>55,92; 210,15</t>
+          <t>61,65; 224,05</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>-16,4; 70,23</t>
+          <t>-15,6; 67,0</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>-47,35; 15,74</t>
+          <t>-47,24; 13,97</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>50,2; 769,07</t>
+          <t>59,65; 829,14</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>-7,9; 55,27</t>
+          <t>-7,88; 52,86</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>-47,93; -3,59</t>
+          <t>-47,15; -3,7</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>82,47; 630,52</t>
+          <t>83,65; 763,91</t>
         </is>
       </c>
     </row>
@@ -1325,47 +1325,47 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>0,18; 5,7</t>
+          <t>0,15; 5,47</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>-1,17; 3,99</t>
+          <t>-1,25; 3,68</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>2,11; 7,53</t>
+          <t>1,91; 7,46</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>-0,02; 5,42</t>
+          <t>-0,13; 5,3</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>-2,65; 2,52</t>
+          <t>-2,76; 2,79</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>-1,47; 4,1</t>
+          <t>-1,27; 4,38</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>0,6; 4,68</t>
+          <t>0,65; 4,57</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
         <is>
-          <t>-1,19; 2,53</t>
+          <t>-1,11; 2,53</t>
         </is>
       </c>
       <c r="K17" s="2" t="inlineStr">
         <is>
-          <t>1,17; 5,05</t>
+          <t>0,92; 4,92</t>
         </is>
       </c>
     </row>
@@ -1431,47 +1431,47 @@
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
-          <t>1,93; 98,01</t>
+          <t>0,66; 90,19</t>
         </is>
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>-13,19; 64,86</t>
+          <t>-15,01; 58,49</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>25,64; 125,19</t>
+          <t>21,7; 124,68</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>-0,11; 63,19</t>
+          <t>-1,37; 60,99</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
         <is>
-          <t>-24,11; 29,48</t>
+          <t>-24,5; 32,43</t>
         </is>
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>-11,61; 48,57</t>
+          <t>-10,17; 51,26</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>6,54; 61,31</t>
+          <t>7,29; 59,47</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
         <is>
-          <t>-12,52; 33,81</t>
+          <t>-12,14; 32,94</t>
         </is>
       </c>
       <c r="K19" s="2" t="inlineStr">
         <is>
-          <t>11,58; 64,88</t>
+          <t>9,6; 62,96</t>
         </is>
       </c>
     </row>
@@ -1541,47 +1541,47 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>1,48; 4,3</t>
+          <t>1,46; 4,22</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>-0,98; 1,73</t>
+          <t>-1,02; 1,57</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>3,34; 8,03</t>
+          <t>3,16; 8,11</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>2,0; 4,86</t>
+          <t>2,08; 4,94</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
         <is>
-          <t>-0,67; 2,09</t>
+          <t>-0,7; 2,16</t>
         </is>
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>5,29; 24,61</t>
+          <t>5,37; 25,2</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>2,28; 4,16</t>
+          <t>2,26; 4,15</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
         <is>
-          <t>-0,43; 1,41</t>
+          <t>-0,44; 1,6</t>
         </is>
       </c>
       <c r="K21" s="2" t="inlineStr">
         <is>
-          <t>5,6; 20,5</t>
+          <t>5,62; 18,78</t>
         </is>
       </c>
     </row>
@@ -1647,47 +1647,47 @@
       </c>
       <c r="C23" s="2" t="inlineStr">
         <is>
-          <t>20,37; 70,69</t>
+          <t>19,79; 70,89</t>
         </is>
       </c>
       <c r="D23" s="2" t="inlineStr">
         <is>
-          <t>-13,5; 28,49</t>
+          <t>-13,91; 25,86</t>
         </is>
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>47,85; 127,85</t>
+          <t>48,36; 132,68</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>22,41; 65,67</t>
+          <t>23,38; 67,25</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
         <is>
-          <t>-7,53; 28,79</t>
+          <t>-8,54; 28,77</t>
         </is>
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>64,3; 322,65</t>
+          <t>63,86; 312,37</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>28,81; 60,41</t>
+          <t>28,79; 60,26</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
         <is>
-          <t>-5,49; 20,43</t>
+          <t>-5,7; 22,29</t>
         </is>
       </c>
       <c r="K23" s="2" t="inlineStr">
         <is>
-          <t>74,06; 262,23</t>
+          <t>75,31; 258,01</t>
         </is>
       </c>
     </row>

--- a/data/trans_camb/P2A_lim_R-Habitat-trans_camb.xlsx
+++ b/data/trans_camb/P2A_lim_R-Habitat-trans_camb.xlsx
@@ -634,7 +634,7 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>9,15</t>
+          <t>8,62</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
@@ -649,7 +649,7 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>7,79</t>
+          <t>8,64</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
@@ -664,7 +664,7 @@
       </c>
       <c r="K4" s="2" t="inlineStr">
         <is>
-          <t>8,43</t>
+          <t>8,64</t>
         </is>
       </c>
     </row>
@@ -677,47 +677,47 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>1,42; 7,15</t>
+          <t>1,5; 7,25</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>1,01; 6,25</t>
+          <t>0,43; 6,0</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>6,22; 12,27</t>
+          <t>5,67; 11,55</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>3,15; 8,98</t>
+          <t>2,85; 9,01</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>0,76; 6,39</t>
+          <t>0,84; 6,14</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>4,44; 10,34</t>
+          <t>6,15; 11,43</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>3,13; 7,29</t>
+          <t>3,09; 7,22</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>1,36; 5,57</t>
+          <t>1,75; 5,64</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>6,08; 10,57</t>
+          <t>6,66; 10,76</t>
         </is>
       </c>
     </row>
@@ -740,7 +740,7 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>176,43%</t>
+          <t>166,26%</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
@@ -755,7 +755,7 @@
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>143,7%</t>
+          <t>159,51%</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
@@ -770,7 +770,7 @@
       </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>159,05%</t>
+          <t>162,9%</t>
         </is>
       </c>
     </row>
@@ -783,47 +783,47 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>20,95; 170,53</t>
+          <t>23,67; 176,87</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>14,88; 150,09</t>
+          <t>5,7; 139,28</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>98,28; 292,8</t>
+          <t>89,01; 288,67</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>45,7; 205,09</t>
+          <t>37,94; 212,77</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>9,28; 146,2</t>
+          <t>11,04; 141,85</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>65,64; 242,37</t>
+          <t>83,33; 266,71</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>49,26; 161,56</t>
+          <t>53,12; 166,67</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>22,22; 125,83</t>
+          <t>27,21; 121,06</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>98,06; 243,4</t>
+          <t>103,04; 232,85</t>
         </is>
       </c>
     </row>
@@ -850,7 +850,7 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>4,34</t>
+          <t>7,03</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
@@ -865,7 +865,7 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>8,33</t>
+          <t>8,19</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
@@ -880,7 +880,7 @@
       </c>
       <c r="K8" s="2" t="inlineStr">
         <is>
-          <t>6,08</t>
+          <t>7,61</t>
         </is>
       </c>
     </row>
@@ -893,47 +893,47 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>-0,03; 5,43</t>
+          <t>0,28; 5,69</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>-2,76; 2,13</t>
+          <t>-2,77; 2,14</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>-1,52; 8,41</t>
+          <t>4,27; 10,08</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>1,54; 6,96</t>
+          <t>1,61; 6,94</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>-1,6; 3,72</t>
+          <t>-1,57; 3,87</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>5,71; 10,82</t>
+          <t>5,46; 10,83</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>1,7; 5,59</t>
+          <t>1,77; 5,45</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>-1,32; 2,23</t>
+          <t>-1,42; 2,12</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>1,88; 8,55</t>
+          <t>5,59; 9,52</t>
         </is>
       </c>
     </row>
@@ -956,7 +956,7 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>61,32%</t>
+          <t>99,26%</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
@@ -971,7 +971,7 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>108,33%</t>
+          <t>106,42%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
@@ -986,7 +986,7 @@
       </c>
       <c r="K10" s="2" t="inlineStr">
         <is>
-          <t>82,29%</t>
+          <t>103,05%</t>
         </is>
       </c>
     </row>
@@ -999,47 +999,47 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>-1,93; 88,0</t>
+          <t>2,58; 96,62</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>-32,51; 37,64</t>
+          <t>-33,2; 36,49</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>-17,6; 133,53</t>
+          <t>50,89; 168,49</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>15,63; 106,42</t>
+          <t>17,22; 109,22</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>-16,72; 61,23</t>
+          <t>-17,87; 60,73</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>62,14; 169,32</t>
+          <t>57,77; 176,04</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>20,39; 85,75</t>
+          <t>21,26; 81,93</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>-15,7; 33,83</t>
+          <t>-17,28; 31,88</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>23,75; 125,67</t>
+          <t>66,03; 147,67</t>
         </is>
       </c>
     </row>
@@ -1066,7 +1066,7 @@
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>8,63</t>
+          <t>8,39</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
@@ -1081,7 +1081,7 @@
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>24,95</t>
+          <t>7,51</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
@@ -1096,7 +1096,7 @@
       </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>18,08</t>
+          <t>7,95</t>
         </is>
       </c>
     </row>
@@ -1109,47 +1109,47 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>-1,36; 4,78</t>
+          <t>-0,99; 4,92</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>-5,28; -0,01</t>
+          <t>-5,15; -0,09</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>5,25; 12,17</t>
+          <t>5,08; 12,03</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>-1,45; 4,76</t>
+          <t>-1,29; 4,65</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>-4,7; 0,95</t>
+          <t>-4,83; 0,97</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>5,08; 60,09</t>
+          <t>4,54; 11,27</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>-0,69; 3,66</t>
+          <t>-0,64; 3,65</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>-4,08; -0,27</t>
+          <t>-4,24; -0,4</t>
         </is>
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>6,75; 44,87</t>
+          <t>5,67; 10,23</t>
         </is>
       </c>
     </row>
@@ -1172,7 +1172,7 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>125,52%</t>
+          <t>122,03%</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
@@ -1187,7 +1187,7 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>291,83%</t>
+          <t>87,85%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
@@ -1202,7 +1202,7 @@
       </c>
       <c r="K14" s="2" t="inlineStr">
         <is>
-          <t>234,24%</t>
+          <t>103,0%</t>
         </is>
       </c>
     </row>
@@ -1215,47 +1215,47 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>-16,03; 86,55</t>
+          <t>-12,94; 90,45</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>-61,85; 1,86</t>
+          <t>-61,37; -1,47</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>61,65; 224,05</t>
+          <t>57,36; 220,63</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>-15,6; 67,0</t>
+          <t>-14,03; 66,97</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>-47,24; 13,97</t>
+          <t>-46,97; 13,45</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>59,65; 829,14</t>
+          <t>44,65; 163,04</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>-7,88; 52,86</t>
+          <t>-7,59; 56,27</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>-47,15; -3,7</t>
+          <t>-48,23; -5,06</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>83,65; 763,91</t>
+          <t>64,52; 154,64</t>
         </is>
       </c>
     </row>
@@ -1282,7 +1282,7 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>4,54</t>
+          <t>4,17</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
@@ -1297,7 +1297,7 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>1,83</t>
+          <t>2,56</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
@@ -1312,7 +1312,7 @@
       </c>
       <c r="K16" s="2" t="inlineStr">
         <is>
-          <t>3,11</t>
+          <t>3,33</t>
         </is>
       </c>
     </row>
@@ -1325,47 +1325,47 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>0,15; 5,47</t>
+          <t>0,42; 5,39</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>-1,25; 3,68</t>
+          <t>-1,09; 3,89</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>1,91; 7,46</t>
+          <t>1,66; 6,84</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>-0,13; 5,3</t>
+          <t>-0,11; 5,46</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>-2,76; 2,79</t>
+          <t>-2,68; 2,67</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>-1,27; 4,38</t>
+          <t>0,25; 5,08</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>0,65; 4,57</t>
+          <t>0,7; 4,62</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
         <is>
-          <t>-1,11; 2,53</t>
+          <t>-1,07; 2,31</t>
         </is>
       </c>
       <c r="K17" s="2" t="inlineStr">
         <is>
-          <t>0,92; 4,92</t>
+          <t>1,69; 5,07</t>
         </is>
       </c>
     </row>
@@ -1388,7 +1388,7 @@
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>63,31%</t>
+          <t>58,18%</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
@@ -1403,7 +1403,7 @@
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>18,67%</t>
+          <t>26,14%</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
@@ -1418,7 +1418,7 @@
       </c>
       <c r="K18" s="2" t="inlineStr">
         <is>
-          <t>36,48%</t>
+          <t>39,04%</t>
         </is>
       </c>
     </row>
@@ -1431,47 +1431,47 @@
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
-          <t>0,66; 90,19</t>
+          <t>5,01; 89,86</t>
         </is>
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>-15,01; 58,49</t>
+          <t>-13,47; 63,55</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>21,7; 124,68</t>
+          <t>19,61; 114,03</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>-1,37; 60,99</t>
+          <t>-1,54; 64,28</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
         <is>
-          <t>-24,5; 32,43</t>
+          <t>-24,89; 32,22</t>
         </is>
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>-10,17; 51,26</t>
+          <t>1,99; 60,2</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>7,29; 59,47</t>
+          <t>7,38; 57,9</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
         <is>
-          <t>-12,14; 32,94</t>
+          <t>-10,93; 29,94</t>
         </is>
       </c>
       <c r="K19" s="2" t="inlineStr">
         <is>
-          <t>9,6; 62,96</t>
+          <t>17,61; 64,66</t>
         </is>
       </c>
     </row>
@@ -1498,7 +1498,7 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>6,2</t>
+          <t>6,88</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
@@ -1513,7 +1513,7 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>10,54</t>
+          <t>6,46</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
@@ -1528,7 +1528,7 @@
       </c>
       <c r="K20" s="2" t="inlineStr">
         <is>
-          <t>8,46</t>
+          <t>6,67</t>
         </is>
       </c>
     </row>
@@ -1541,47 +1541,47 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>1,46; 4,22</t>
+          <t>1,45; 4,24</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>-1,02; 1,57</t>
+          <t>-0,89; 1,7</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>3,16; 8,11</t>
+          <t>5,36; 8,39</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>2,08; 4,94</t>
+          <t>2,02; 4,96</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
         <is>
-          <t>-0,7; 2,16</t>
+          <t>-0,57; 2,03</t>
         </is>
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>5,37; 25,2</t>
+          <t>5,06; 7,77</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>2,26; 4,15</t>
+          <t>2,17; 4,11</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
         <is>
-          <t>-0,44; 1,6</t>
+          <t>-0,39; 1,48</t>
         </is>
       </c>
       <c r="K21" s="2" t="inlineStr">
         <is>
-          <t>5,62; 18,78</t>
+          <t>5,63; 7,76</t>
         </is>
       </c>
     </row>
@@ -1604,7 +1604,7 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>93,13%</t>
+          <t>103,25%</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
@@ -1619,7 +1619,7 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>131,01%</t>
+          <t>80,29%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
@@ -1634,7 +1634,7 @@
       </c>
       <c r="K22" s="2" t="inlineStr">
         <is>
-          <t>114,93%</t>
+          <t>90,6%</t>
         </is>
       </c>
     </row>
@@ -1647,47 +1647,47 @@
       </c>
       <c r="C23" s="2" t="inlineStr">
         <is>
-          <t>19,79; 70,89</t>
+          <t>19,54; 68,27</t>
         </is>
       </c>
       <c r="D23" s="2" t="inlineStr">
         <is>
-          <t>-13,91; 25,86</t>
+          <t>-12,17; 27,67</t>
         </is>
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>48,36; 132,68</t>
+          <t>72,44; 139,49</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>23,38; 67,25</t>
+          <t>22,48; 65,7</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
         <is>
-          <t>-8,54; 28,77</t>
+          <t>-6,88; 27,78</t>
         </is>
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>63,86; 312,37</t>
+          <t>56,08; 105,59</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>28,79; 60,26</t>
+          <t>27,61; 59,31</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
         <is>
-          <t>-5,7; 22,29</t>
+          <t>-5,01; 21,55</t>
         </is>
       </c>
       <c r="K23" s="2" t="inlineStr">
         <is>
-          <t>75,31; 258,01</t>
+          <t>71,56; 113,19</t>
         </is>
       </c>
     </row>

--- a/data/trans_camb/P2A_lim_R-Habitat-trans_camb.xlsx
+++ b/data/trans_camb/P2A_lim_R-Habitat-trans_camb.xlsx
@@ -523,7 +523,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Hogares con personas con alguna limitación</t>
+          <t>Población que convive con personas con alguna limitación (física, sensorial o psíquica)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
